--- a/data/trans_bre/P1412-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1412-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-42,5%</t>
+          <t>-36,0%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,24</t>
+          <t>-0,8; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,7</t>
+          <t>-1,63; 0,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,13</t>
+          <t>-2,25; 0,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 144,64</t>
+          <t>-42,94; 148,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 75,88</t>
+          <t>-68,94; 65,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 12,4</t>
+          <t>-68,85; 24,37</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-42,56%</t>
+          <t>-36,68%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; -0,03</t>
+          <t>-0,81; -0,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,18</t>
+          <t>-0,55; 0,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,1</t>
+          <t>-0,66; 0,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,13</t>
+          <t>-100,0; 41,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 136,87</t>
+          <t>-88,03; 143,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,15; 32,87</t>
+          <t>-72,4; 31,3</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-80,24%</t>
+          <t>-81,14%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,19</t>
+          <t>-1,87; 0,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,18</t>
+          <t>-1,5; -0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,05</t>
+          <t>-100,0; 6,21</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-39,38%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,43</t>
+          <t>-0,38; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,17</t>
+          <t>-0,62; 0,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; -0,05</t>
+          <t>-0,74; -0,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 95,95</t>
+          <t>-43,85; 89,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 35,05</t>
+          <t>-64,03; 28,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,44; -7,09</t>
+          <t>-61,27; -4,87</t>
         </is>
       </c>
     </row>
